--- a/ABA_mining/outputs/eval/task3/price/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
@@ -541,16 +541,16 @@
         <v>44</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8944723618090452</v>
+        <v>0.894472</v>
       </c>
       <c r="M2" t="n">
         <v>0.89</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8922305764411028</v>
+        <v>0.89223</v>
       </c>
       <c r="O2" t="n">
-        <v>0.810989010989011</v>
+        <v>0.810989</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +600,16 @@
         <v>44</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8944723618090452</v>
+        <v>0.894472</v>
       </c>
       <c r="M3" t="n">
         <v>0.89</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8922305764411028</v>
+        <v>0.89223</v>
       </c>
       <c r="O3" t="n">
-        <v>0.810989010989011</v>
+        <v>0.810989</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8942065491183879</v>
+        <v>0.894207</v>
       </c>
       <c r="M4" t="n">
         <v>0.8875</v>
       </c>
       <c r="N4" t="n">
-        <v>0.890840652446675</v>
+        <v>0.890841</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8087912087912088</v>
+        <v>0.808791</v>
       </c>
     </row>
   </sheetData>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8943839061190276</v>
+        <v>0.894384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8891666666666667</v>
+        <v>0.889167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8917676556623484</v>
+        <v>0.891768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8102564102564103</v>
+        <v>0.810256</v>
       </c>
       <c r="J2" t="n">
         <v>1365</v>
